--- a/docs/test_papers_data_sources.xlsx
+++ b/docs/test_papers_data_sources.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="17100"/>
+    <workbookView windowWidth="26860" windowHeight="16560"/>
   </bookViews>
   <sheets>
     <sheet name="Detailed Data Sources" sheetId="1" r:id="rId1"/>
@@ -141,12 +141,24 @@
     <t>Frazzini &amp; Pedersen (2014)</t>
   </si>
   <si>
-    <t>CRSP (US equities, daily)
+    <r>
+      <t xml:space="preserve">CRSP (US equities, daily)
 Xpressfeed Global (international equities)
 CRSP US Treasury Database (bonds)
 Kenneth French data library (SMB/HML/UMD)
 WRDS (liquidity risk factor)
-MSCI local indices</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MSCI local indices</t>
+    </r>
   </si>
   <si>
     <t>US equities: Jan 1926 - Mar 2012
@@ -172,11 +184,33 @@
     <t>Hirshleifer, Hsu &amp; Li (2012)</t>
   </si>
   <si>
-    <t>Compustat (accounting)
+    <r>
+      <t xml:space="preserve">Compustat (accounting)
 CRSP (returns)
-NBER Patent Database (Hall, Jaffe &amp; Trajtenberg 2001 version)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NBER Patent Database (Hall, Jaffe &amp; Trajtenberg 2001 version)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 IBES (analyst coverage, supplementary)
 Thomson Reuters Institutional (13F) Holdings (ownership, supplementary)</t>
+    </r>
   </si>
   <si>
     <t>NBER patent data: Jan 1976 - Dec 2006 (patents granted)</t>
@@ -249,9 +283,31 @@
     <t>Valta</t>
   </si>
   <si>
-    <t>CRSP (monthly stock data)
-Standard &amp; Poor's Compustat (annual financials)
+    <r>
+      <t xml:space="preserve">CRSP (monthly stock data)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard &amp; Poor's Compustat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (annual financials)
 Thomson Financial Ownership Database (institutional ownership)</t>
+    </r>
   </si>
   <si>
     <t>1985 - 2012</t>
@@ -301,10 +357,32 @@
     <t>An, Ang, Bali &amp; Cakici (2013)</t>
   </si>
   <si>
-    <t>OptionMetrics (Volatility Surface)
+    <r>
+      <t>OptionMetrics (Volatility Surface)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 CRSP (stock returns)
 COMPUSTAT (accounting/balance sheet)
-Ibbotson (risk-free rate)</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ibbotson (risk-free rate)</t>
+    </r>
   </si>
   <si>
     <t>Jan 1996 - Dec 2011</t>
@@ -431,7 +509,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -905,19 +983,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -926,7 +1004,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1050,12 +1128,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1543,7 +1627,7 @@
       <c r="C5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1572,7 +1656,7 @@
       <c r="C6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1659,7 +1743,7 @@
       <c r="C9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -1717,7 +1801,7 @@
       <c r="C11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E11" s="2" t="s">
